--- a/2026_dashboard.xlsx
+++ b/2026_dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwchoi\.gemini\antigravity\scratch\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6AA15F5-D1ED-4D76-9CF4-085CA309DE6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D71230-10D1-43AE-BDBB-6E5F215204E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30285" yWindow="1275" windowWidth="25770" windowHeight="13380" xr2:uid="{372AB101-DDC1-4D0A-9680-BFBF2765E290}"/>
+    <workbookView xWindow="2145" yWindow="1050" windowWidth="25770" windowHeight="13380" xr2:uid="{372AB101-DDC1-4D0A-9680-BFBF2765E290}"/>
   </bookViews>
   <sheets>
     <sheet name="매출 속성 (2)" sheetId="2" r:id="rId1"/>
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="29">
-        <v>2222222</v>
+        <v>0</v>
       </c>
       <c r="J3" s="29">
         <v>0</v>

--- a/2026_dashboard.xlsx
+++ b/2026_dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwchoi\.gemini\antigravity\scratch\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D475C858-3DCE-4479-9A4C-C8AD769FEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED67BA9-6CEF-41A6-918A-ABD4BE91EA9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2145" yWindow="1050" windowWidth="25770" windowHeight="13380" xr2:uid="{372AB101-DDC1-4D0A-9680-BFBF2765E290}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="34">
   <si>
     <t>구분</t>
   </si>
@@ -153,6 +153,14 @@
   </si>
   <si>
     <t>쿠팡 실적</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>네이버 목표</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>네이버 실적</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -397,7 +405,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -485,6 +493,12 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -524,10 +538,16 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1100,25 +1120,25 @@
       <c r="F6" s="6">
         <v>131985130.27563205</v>
       </c>
-      <c r="G6" s="42">
+      <c r="G6" s="29">
         <v>394786021.99495518</v>
       </c>
-      <c r="H6" s="42">
+      <c r="H6" s="29">
         <v>356113852.83867455</v>
       </c>
-      <c r="I6" s="42">
+      <c r="I6" s="29">
         <v>633076526.71854794</v>
       </c>
-      <c r="J6" s="42">
+      <c r="J6" s="29">
         <v>197086680.85687456</v>
       </c>
-      <c r="K6" s="42">
+      <c r="K6" s="29">
         <v>215347577.16981396</v>
       </c>
-      <c r="L6" s="42">
+      <c r="L6" s="29">
         <v>356618433.32053941</v>
       </c>
-      <c r="M6" s="42">
+      <c r="M6" s="29">
         <v>466482667.94791228</v>
       </c>
     </row>
@@ -1141,36 +1161,82 @@
       <c r="F7" s="3">
         <v>0</v>
       </c>
-      <c r="G7" s="43">
+      <c r="G7" s="30">
         <v>22222</v>
       </c>
-      <c r="H7" s="43">
-        <v>0</v>
-      </c>
-      <c r="I7" s="43">
-        <v>0</v>
-      </c>
-      <c r="J7" s="43">
-        <v>0</v>
-      </c>
-      <c r="K7" s="43">
-        <v>0</v>
-      </c>
-      <c r="L7" s="43">
-        <v>0</v>
-      </c>
-      <c r="M7" s="43">
+      <c r="H7" s="30">
+        <v>0</v>
+      </c>
+      <c r="I7" s="30">
+        <v>0</v>
+      </c>
+      <c r="J7" s="30">
+        <v>0</v>
+      </c>
+      <c r="K7" s="30">
+        <v>0</v>
+      </c>
+      <c r="L7" s="30">
+        <v>0</v>
+      </c>
+      <c r="M7" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B8" s="8"/>
-      <c r="C8" s="7"/>
+      <c r="A8" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="8">
+        <v>333333</v>
+      </c>
+      <c r="C8" s="7">
+        <v>3333</v>
+      </c>
+      <c r="D8" s="45">
+        <v>3333</v>
+      </c>
+      <c r="E8" s="45">
+        <v>3333</v>
+      </c>
+      <c r="I8" s="46">
+        <v>333</v>
+      </c>
+      <c r="K8" s="46">
+        <v>3333</v>
+      </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="7"/>
+      <c r="A9" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="8">
+        <v>666</v>
+      </c>
+      <c r="C9" s="8">
+        <v>66</v>
+      </c>
+      <c r="D9" s="7">
+        <v>666</v>
+      </c>
+      <c r="F9">
+        <v>666</v>
+      </c>
+      <c r="G9">
+        <v>6666</v>
+      </c>
+      <c r="H9">
+        <v>66</v>
+      </c>
+      <c r="I9" s="47">
+        <v>6</v>
+      </c>
+      <c r="J9">
+        <v>6</v>
+      </c>
+      <c r="K9" s="47">
+        <v>66</v>
+      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B10" s="8"/>
@@ -1196,43 +1262,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-      <c r="S1" s="29"/>
-      <c r="T1" s="29"/>
-      <c r="U1" s="29"/>
-      <c r="V1" s="29"/>
-      <c r="W1" s="29"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="29"/>
-      <c r="AA1" s="29"/>
-      <c r="AB1" s="29"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="31"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="31"/>
+      <c r="Z1" s="31"/>
+      <c r="AA1" s="31"/>
+      <c r="AB1" s="31"/>
     </row>
     <row r="2" spans="2:29" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:29" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="31"/>
+      <c r="B3" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="32"/>
+      <c r="D3" s="33"/>
       <c r="E3" s="11" t="s">
         <v>9</v>
       </c>
@@ -1307,10 +1373,10 @@
       </c>
     </row>
     <row r="4" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="36" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="24" t="s">
@@ -1406,8 +1472,8 @@
       </c>
     </row>
     <row r="5" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="40"/>
-      <c r="C5" s="35"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="37"/>
       <c r="D5" s="25" t="s">
         <v>25</v>
       </c>
@@ -1474,7 +1540,7 @@
       <c r="AC5" s="4"/>
     </row>
     <row r="6" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="40"/>
+      <c r="B6" s="42"/>
       <c r="C6" s="9" t="s">
         <v>20</v>
       </c>
@@ -1580,8 +1646,8 @@
       <c r="AC6" s="4"/>
     </row>
     <row r="7" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="40"/>
-      <c r="C7" s="34" t="s">
+      <c r="B7" s="42"/>
+      <c r="C7" s="36" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="24" t="s">
@@ -1677,8 +1743,8 @@
       </c>
     </row>
     <row r="8" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="40"/>
-      <c r="C8" s="35"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="37"/>
       <c r="D8" s="25" t="s">
         <v>25</v>
       </c>
@@ -1745,7 +1811,7 @@
       <c r="AC8" s="4"/>
     </row>
     <row r="9" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="40"/>
+      <c r="B9" s="42"/>
       <c r="C9" s="9" t="s">
         <v>20</v>
       </c>
@@ -1851,8 +1917,8 @@
       <c r="AC9" s="4"/>
     </row>
     <row r="10" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="40"/>
-      <c r="C10" s="34" t="s">
+      <c r="B10" s="42"/>
+      <c r="C10" s="36" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="24" t="s">
@@ -1948,8 +2014,8 @@
       </c>
     </row>
     <row r="11" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="40"/>
-      <c r="C11" s="35"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="37"/>
       <c r="D11" s="25" t="s">
         <v>25</v>
       </c>
@@ -2015,7 +2081,7 @@
       </c>
     </row>
     <row r="12" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="41"/>
+      <c r="B12" s="43"/>
       <c r="C12" s="2" t="s">
         <v>20</v>
       </c>
@@ -2120,11 +2186,11 @@
       </c>
     </row>
     <row r="13" spans="2:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="37"/>
-      <c r="D13" s="38"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="40"/>
       <c r="E13" s="15">
         <f>E4+E7+E10</f>
         <v>606065365.68358994</v>
@@ -2223,11 +2289,11 @@
       </c>
     </row>
     <row r="14" spans="2:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="32"/>
-      <c r="D14" s="33"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="35"/>
       <c r="E14" s="26">
         <f>E5+E8+E11</f>
         <v>614044688</v>

--- a/2026_dashboard.xlsx
+++ b/2026_dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwchoi\.gemini\antigravity\scratch\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF926FFC-FF1C-4786-B805-469984235AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DE418E7-924B-4555-9D99-1E5E242F3693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2145" yWindow="1050" windowWidth="25770" windowHeight="13380" xr2:uid="{372AB101-DDC1-4D0A-9680-BFBF2765E290}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>8월</t>
   </si>
@@ -97,14 +97,6 @@
   </si>
   <si>
     <t>쿠팡 실적</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>네이버 목표</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>네이버 실적</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -185,7 +177,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -208,17 +200,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -228,7 +209,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -254,18 +235,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -608,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BA1C98D-3AA8-41E9-86D6-2B57E0D38592}">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
@@ -714,9 +683,7 @@
       <c r="F3" s="2">
         <v>0</v>
       </c>
-      <c r="G3" s="2">
-        <v>22222</v>
-      </c>
+      <c r="G3" s="2"/>
       <c r="H3" s="2">
         <v>0</v>
       </c>
@@ -796,9 +763,7 @@
       <c r="F5" s="2">
         <v>0</v>
       </c>
-      <c r="G5" s="2">
-        <v>22222</v>
-      </c>
+      <c r="G5" s="2"/>
       <c r="H5" s="2">
         <v>0</v>
       </c>
@@ -878,9 +843,7 @@
       <c r="F7" s="2">
         <v>0</v>
       </c>
-      <c r="G7" s="8">
-        <v>22222</v>
-      </c>
+      <c r="G7" s="8"/>
       <c r="H7" s="8">
         <v>0</v>
       </c>
@@ -901,63 +864,8 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="5">
-        <v>333333</v>
-      </c>
-      <c r="C8" s="4">
-        <v>3333</v>
-      </c>
-      <c r="D8" s="10">
-        <v>3333</v>
-      </c>
-      <c r="E8" s="10">
-        <v>3333</v>
-      </c>
-      <c r="I8" s="11">
-        <v>333</v>
-      </c>
-      <c r="K8" s="11">
-        <v>3333</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="5">
-        <v>666</v>
-      </c>
-      <c r="C9" s="5">
-        <v>66</v>
-      </c>
-      <c r="D9" s="4">
-        <v>666</v>
-      </c>
-      <c r="F9">
-        <v>666</v>
-      </c>
-      <c r="G9">
-        <v>6666</v>
-      </c>
-      <c r="H9">
-        <v>66</v>
-      </c>
-      <c r="I9" s="12">
-        <v>6</v>
-      </c>
-      <c r="J9">
-        <v>6</v>
-      </c>
-      <c r="K9" s="12">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B10" s="5"/>
-      <c r="D10" s="4"/>
+      <c r="B8" s="5"/>
+      <c r="D8" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/2026_dashboard.xlsx
+++ b/2026_dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwchoi\.gemini\antigravity\scratch\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DE418E7-924B-4555-9D99-1E5E242F3693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5293809-A5ED-4E61-AA4B-E0C16B9C15EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2145" yWindow="1050" windowWidth="25770" windowHeight="13380" xr2:uid="{372AB101-DDC1-4D0A-9680-BFBF2765E290}"/>
+    <workbookView xWindow="33900" yWindow="1260" windowWidth="25770" windowHeight="13380" xr2:uid="{372AB101-DDC1-4D0A-9680-BFBF2765E290}"/>
   </bookViews>
   <sheets>
     <sheet name="매출 데이터" sheetId="2" r:id="rId1"/>
@@ -675,7 +675,7 @@
         <v>307671200</v>
       </c>
       <c r="D3" s="2">
-        <v>207081610</v>
+        <v>244061945</v>
       </c>
       <c r="E3" s="2">
         <v>0</v>
@@ -683,7 +683,9 @@
       <c r="F3" s="2">
         <v>0</v>
       </c>
-      <c r="G3" s="2"/>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
       <c r="H3" s="2">
         <v>0</v>
       </c>
@@ -755,7 +757,7 @@
         <v>90613312</v>
       </c>
       <c r="D5" s="2">
-        <v>75975344</v>
+        <v>94701456</v>
       </c>
       <c r="E5" s="2">
         <v>0</v>
@@ -763,7 +765,9 @@
       <c r="F5" s="2">
         <v>0</v>
       </c>
-      <c r="G5" s="2"/>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
       <c r="H5" s="2">
         <v>0</v>
       </c>
@@ -843,7 +847,9 @@
       <c r="F7" s="2">
         <v>0</v>
       </c>
-      <c r="G7" s="8"/>
+      <c r="G7" s="8">
+        <v>0</v>
+      </c>
       <c r="H7" s="8">
         <v>0</v>
       </c>
